--- a/0_0_Data/3_Naive_Forecaster_Data/1_YoY_Forecast_Vectors/forecast_series_PRIVCON_yoy_AVERAGE_FULL_9_summer.xlsx
+++ b/0_0_Data/3_Naive_Forecaster_Data/1_YoY_Forecast_Vectors/forecast_series_PRIVCON_yoy_AVERAGE_FULL_9_summer.xlsx
@@ -392,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -414,305 +414,350 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>39583</v>
+        <v>38496</v>
       </c>
       <c r="B2">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="D2">
-        <v>2009</v>
-      </c>
-      <c r="E2">
-        <v>0.2331560026455293</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>39948</v>
+        <v>38860</v>
       </c>
       <c r="B3">
-        <v>2009</v>
-      </c>
-      <c r="C3">
-        <v>0.02099249989730989</v>
+        <v>2006</v>
       </c>
       <c r="D3">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="E3">
-        <v>0.2658381086248385</v>
+        <v>1.478800353636278</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>40310</v>
+        <v>39226</v>
       </c>
       <c r="B4">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="C4">
-        <v>-1.307603585337391</v>
+        <v>2.388329787422805</v>
       </c>
       <c r="D4">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="E4">
-        <v>-0.3190550775459045</v>
+        <v>2.054906384059163</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>40676</v>
+        <v>39595</v>
       </c>
       <c r="B5">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="C5">
-        <v>1.669611657667169</v>
+        <v>1.400922024469864</v>
       </c>
       <c r="D5">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="E5">
-        <v>0.5111763828599347</v>
+        <v>1.752823409606341</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>41044</v>
+        <v>39959</v>
       </c>
       <c r="B6">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="C6">
-        <v>0.911388480980535</v>
+        <v>0.9777593537953155</v>
       </c>
       <c r="D6">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="E6">
-        <v>0.6030710844623588</v>
+        <v>1.505996600083859</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>41409</v>
+        <v>40319</v>
       </c>
       <c r="B7">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="C7">
-        <v>0.5781767497138546</v>
+        <v>2.222831442988071</v>
       </c>
       <c r="D7">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="E7">
-        <v>0.7638490973419954</v>
+        <v>1.864287960344368</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>41774</v>
+        <v>40687</v>
       </c>
       <c r="B8">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="C8">
-        <v>0.9983422690224231</v>
+        <v>1.764446094428029</v>
       </c>
       <c r="D8">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="E8">
-        <v>0.8472407659630088</v>
+        <v>1.90841960758521</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>42137</v>
+        <v>41053</v>
       </c>
       <c r="B9">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="C9">
-        <v>2.043582053676651</v>
+        <v>1.615295332434563</v>
       </c>
       <c r="D9">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="E9">
-        <v>0.922870897584871</v>
+        <v>1.618714658368936</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>42503</v>
+        <v>41418</v>
       </c>
       <c r="B10">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="C10">
-        <v>1.627179431907866</v>
+        <v>0.7568928795189001</v>
       </c>
       <c r="D10">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="E10">
-        <v>0.9048417649844875</v>
+        <v>1.465375618478459</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>42867</v>
+        <v>41782</v>
       </c>
       <c r="B11">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="C11">
-        <v>1.275170630186784</v>
+        <v>0.6410555646616967</v>
       </c>
       <c r="D11">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="E11">
-        <v>0.9367370402057817</v>
+        <v>1.549249030274691</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>43235</v>
+        <v>42146</v>
       </c>
       <c r="B12">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="C12">
-        <v>1.12840110321426</v>
+        <v>1.970233107138508</v>
       </c>
       <c r="D12">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="E12">
-        <v>1.016857026310336</v>
+        <v>1.708622549409577</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>43600</v>
+        <v>42514</v>
       </c>
       <c r="B13">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C13">
-        <v>1.51898250939253</v>
+        <v>2.589364232032954</v>
       </c>
       <c r="D13">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="E13">
-        <v>1.237919511659746</v>
+        <v>1.719212499841682</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>43966</v>
+        <v>42878</v>
       </c>
       <c r="B14">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C14">
-        <v>-1.803908062678516</v>
+        <v>1.729122882326695</v>
       </c>
       <c r="D14">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="E14">
-        <v>-0.1348226305034728</v>
+        <v>1.759400999078675</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>44341</v>
+        <v>43244</v>
       </c>
       <c r="B15">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="C15">
-        <v>-5.03363841893295</v>
+        <v>1.053253701890378</v>
       </c>
       <c r="D15">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="E15">
-        <v>-1.150039807777148</v>
+        <v>1.498847912172341</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>44706</v>
+        <v>43608</v>
       </c>
       <c r="B16">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C16">
-        <v>3.806533520739741</v>
+        <v>1.512087606596935</v>
       </c>
       <c r="D16">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="E16">
-        <v>0.6742812297244161</v>
+        <v>1.572219740256986</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>45071</v>
+        <v>43976</v>
       </c>
       <c r="B17">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="C17">
-        <v>-1.12666423816119</v>
+        <v>2.177023921605392</v>
       </c>
       <c r="D17">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E17">
-        <v>0.3593347800071145</v>
+        <v>1.892590492895452</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>45436</v>
+        <v>44341</v>
       </c>
       <c r="B18">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="C18">
-        <v>0.2013114615211142</v>
+        <v>2.317224818653352</v>
       </c>
       <c r="D18">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="E18">
-        <v>0.5722808921970746</v>
+        <v>1.918363145155833</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
+        <v>44706</v>
+      </c>
+      <c r="B19">
+        <v>2022</v>
+      </c>
+      <c r="C19">
+        <v>0.3845663659276299</v>
+      </c>
+      <c r="D19">
+        <v>2023</v>
+      </c>
+      <c r="E19">
+        <v>1.874923804206174</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="2">
+        <v>45071</v>
+      </c>
+      <c r="B20">
+        <v>2023</v>
+      </c>
+      <c r="C20">
+        <v>-3.594661838437851</v>
+      </c>
+      <c r="D20">
+        <v>2024</v>
+      </c>
+      <c r="E20">
+        <v>0.4241841204802643</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="2">
+        <v>45436</v>
+      </c>
+      <c r="B21">
+        <v>2024</v>
+      </c>
+      <c r="C21">
+        <v>1.360829857501122</v>
+      </c>
+      <c r="D21">
+        <v>2025</v>
+      </c>
+      <c r="E21">
+        <v>1.685192241308342</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="2">
         <v>45800</v>
       </c>
-      <c r="B19">
+      <c r="B22">
         <v>2025</v>
       </c>
-      <c r="C19">
-        <v>0.9834415437034227</v>
-      </c>
-      <c r="D19">
+      <c r="C22">
+        <v>2.309321499638206</v>
+      </c>
+      <c r="D22">
         <v>2026</v>
       </c>
-      <c r="E19">
-        <v>0.8328031391292345</v>
+      <c r="E22">
+        <v>1.911286721384009</v>
       </c>
     </row>
   </sheetData>
